--- a/소스 설명/소스확인용_260723.xlsx
+++ b/소스 설명/소스확인용_260723.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phc\source\repos\CowAuctionSmall 비쥬얼라이즈 9.0 260707_정읍\소스 설명\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phc\source\repos\CowAuctionSmall 비쥬얼라이즈 9.0 260724_춘천\소스 설명\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F7E4C8-0C6B-4DD5-9C06-A381B4193562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDA5200-8A07-469B-9575-03500D775BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="5715" windowWidth="21150" windowHeight="15270" activeTab="1" xr2:uid="{2B249932-EB5B-4289-9354-1DACC72D269B}"/>
+    <workbookView xWindow="1635" yWindow="0" windowWidth="21450" windowHeight="20985" activeTab="1" xr2:uid="{2B249932-EB5B-4289-9354-1DACC72D269B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="216">
   <si>
     <t>IsShowQQuri</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1343,6 +1343,232 @@
          - 낙찰 페이지  ChuncheonSold.xaml 낙찰 화면
          - 유찰 페이지  ChuncheonUnSold.xaml 유찰 화면
          - AnimalParseData.cs -&gt; 춘천 축협 코드일 경우 친자일치 값을 강제로 비활성화("-") 처리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>양평</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해남진도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>횡성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>화순</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 낙찰 페이지 JecheonDanyangSold.xaml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제천단양</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예천</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 낙찰 페이지 QQuriSold_v3.xaml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>음성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>익산군산</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 유찰 페이지 IksanGunsanUnSold.xaml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 낙찰 페이지 Standard_non_X_Sold_v3.xaml 미작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 유찰 페이지 NamwonUnSold.xaml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 낙찰 페이지 SengjuSold.xaml
+ - 유찰 페이지 SanjuUnSold.xaml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 낙찰 페이지 BothBidderSold.xaml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 낙찰 페이지 YangpyeongSold.xaml
+ - 유찰 페이지 YangpyeongUnSold.xaml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 러닝 페이지 HaenamJindo.xaml
+ - 낙찰 페이지 HaenamJindoSold.xaml
+ - 유찰 페이지 HaenamJindoUnSold.xaml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 러닝 페이지 Hwasun.xaml
+ - 낙찰 페이지 HwasunSold.xaml
+ - 유찰 페이지 HwasunUnSold.xaml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 러닝 페이지 Hwasun.xaml
+ - 낙찰 페이지 .xaml
+ - 유찰 페이지 .xaml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 러닝 페이지 Jeonju.xaml
+ - 유찰 페이지 JeonjuUnSold.xaml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 러닝 페이지 MokpoMuanSinan.xaml
+ - 낙찰 페이지 MokpoMuanSinanSold.xaml 미작성
+ - 유찰 페이지 MokpoMuanSinanUnSold.xaml 미작성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목무신</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 유전 페이지 Eumseong2.xaml
+ - 유찰 페이지 EumseongUnSold.xaml
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 러닝 페이지 HoengseongRun.xaml
+ - 유전 페이지 Eumseong2.xaml
+ - 유전 페이지 Hoengseong.xaml
+ - 유전 페이지 TestRunning2.xaml
+ - 낙찰 페이지 HoengseongSold.xaml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 유전 페이지 AuctionRunning2.xaml
+ - 유전 페이지 AuctionRunning2_3.xaml  번식우
+ - 유전 페이지 AuctionRunning3.xaml  농협 유전능력
+ - 유전 페이지 AuctionRunning4.xaml   농협 유전능력(번식우)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 비고 페이지 RunningNoteHost128.xaml  친자일치 여부 표함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 낙찰 페이지 QQuriSold.xaml
+ - 낙찰 페이지 QQuriSold_Weight.xaml  
+ - 낙찰 페이지 QQuriSold_v2.xaml
+ - 낙찰 페이지 Standard_non_X_Sold.xaml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> - 유찰 페이지 OutLineUnSold.xaml
+ - 유찰 페이지 QQuriUnSold.xaml
+ - 유찰 페이지 Standard_non_X_UnSold.xaml</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - 염소 러닝 페이지 Standard_Goat_Run.xaml</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+ - 염소 낙찰 페이지 GoatSold.xaml
+ - 염소 유찰 페이지 GoatUnSold.xaml</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> - 러닝 페이지 Standard_non_QQuri_Run1.xaml  (IsShowQQuri = N)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - 러닝 페이지 Standard_non_X_Run1.xaml  (IsShowQQuri = X)
+ - 러닝 페이지 StandardQQuri_Run1.xaml  (IsShowQQuri = Y)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> - 러닝 페이지 Yecheon.xaml  중량,육종 선택적용
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="8"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - 러닝 페이지 Yecheon_v2.xaml  뿌리농가 적용 (무진장 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> - 낙찰 페이지 YecheonSold.xaml
+ - 유찰 페이지 YecheonUnSold.xaml</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1353,7 +1579,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1504,6 +1730,22 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1539,7 +1781,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1643,6 +1885,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2697,50 +2945,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>152</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>514518</xdr:colOff>
-      <xdr:row>157</xdr:row>
-      <xdr:rowOff>152568</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="그림 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0EFDD1E-3745-2B4E-E506-D0FBDF63F483}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2057400" y="31851600"/>
-          <a:ext cx="1200318" cy="1200318"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>152</xdr:row>
@@ -2766,7 +2970,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId25"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2810,7 +3014,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId26"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2854,7 +3058,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId27"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2898,7 +3102,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId28"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2907,6 +3111,138 @@
         <a:xfrm>
           <a:off x="4800600" y="21164550"/>
           <a:ext cx="1181265" cy="1219370"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>533570</xdr:colOff>
+      <xdr:row>166</xdr:row>
+      <xdr:rowOff>181146</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="그림 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1BD0596-6058-90E1-A2DF-3A046F81EC23}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId29"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="33737550"/>
+          <a:ext cx="1219370" cy="1228896"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>161</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>533570</xdr:colOff>
+      <xdr:row>166</xdr:row>
+      <xdr:rowOff>190673</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="그림 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B4E73E49-7984-C552-EE05-192D714FF959}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId30"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2057400" y="33737550"/>
+          <a:ext cx="1219370" cy="1238423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>543096</xdr:colOff>
+      <xdr:row>157</xdr:row>
+      <xdr:rowOff>171620</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="그림 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5C03A7A5-F8C2-DD45-85D6-F9E5456AE14E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId31"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2057400" y="31851600"/>
+          <a:ext cx="1228896" cy="1219370"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3724,7 +4060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1563A77A-B264-444D-93AF-F05F701637F8}">
-  <dimension ref="A1:U152"/>
+  <dimension ref="A1:U161"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="8" max="8" width="15.625" bestFit="1" customWidth="1"/>
@@ -3879,6 +4215,11 @@
         <v>1</v>
       </c>
     </row>
+    <row r="161" spans="1:1">
+      <c r="A161" t="s">
+        <v>182</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3888,7 +4229,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99662D38-98ED-4F10-BEB7-30EF02E2278D}">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.375" style="10" customWidth="1"/>
@@ -3959,28 +4300,333 @@
       <c r="B4" s="32">
         <v>8808990656953</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="83.1" customHeight="1"/>
-    <row r="6" spans="1:15" ht="83.1" customHeight="1"/>
-    <row r="7" spans="1:15" ht="83.1" customHeight="1"/>
-    <row r="8" spans="1:15" ht="83.1" customHeight="1"/>
-    <row r="9" spans="1:15" ht="83.1" customHeight="1"/>
-    <row r="10" spans="1:15" ht="83.1" customHeight="1"/>
-    <row r="11" spans="1:15" ht="83.1" customHeight="1"/>
-    <row r="12" spans="1:15" ht="83.1" customHeight="1"/>
-    <row r="13" spans="1:15" ht="83.1" customHeight="1"/>
-    <row r="14" spans="1:15" ht="83.1" customHeight="1"/>
-    <row r="15" spans="1:15" ht="83.1" customHeight="1"/>
-    <row r="16" spans="1:15" ht="83.1" customHeight="1"/>
-    <row r="17" ht="83.1" customHeight="1"/>
-    <row r="18" ht="83.1" customHeight="1"/>
-    <row r="19" ht="83.1" customHeight="1"/>
-    <row r="20" ht="83.1" customHeight="1"/>
-    <row r="21" ht="83.1" customHeight="1"/>
-    <row r="22" ht="83.1" customHeight="1"/>
+      <c r="H4" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+    </row>
+    <row r="5" spans="1:15" ht="83.1" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B5" s="32">
+        <v>8808990643625</v>
+      </c>
+      <c r="H5" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="35"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+    </row>
+    <row r="6" spans="1:15" ht="83.1" customHeight="1">
+      <c r="A6" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H6" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+    </row>
+    <row r="7" spans="1:15" ht="83.1" customHeight="1">
+      <c r="A7" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="H7" s="34" t="s">
+        <v>208</v>
+      </c>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+    </row>
+    <row r="8" spans="1:15" ht="83.1" customHeight="1">
+      <c r="A8" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+    </row>
+    <row r="9" spans="1:15" ht="83.1" customHeight="1">
+      <c r="A9" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>186</v>
+      </c>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
+      <c r="O9" s="35"/>
+    </row>
+    <row r="10" spans="1:15" ht="83.1" customHeight="1">
+      <c r="A10" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="35"/>
+      <c r="M10" s="35"/>
+      <c r="N10" s="35"/>
+      <c r="O10" s="35"/>
+    </row>
+    <row r="11" spans="1:15" ht="83.1" customHeight="1">
+      <c r="H11" s="34" t="s">
+        <v>211</v>
+      </c>
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+      <c r="K11" s="35"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="35"/>
+      <c r="N11" s="35"/>
+      <c r="O11" s="35"/>
+    </row>
+    <row r="12" spans="1:15" ht="83.1" customHeight="1">
+      <c r="H12" s="35" t="s">
+        <v>189</v>
+      </c>
+      <c r="I12" s="35"/>
+      <c r="J12" s="35"/>
+      <c r="K12" s="35"/>
+      <c r="L12" s="35"/>
+      <c r="M12" s="35"/>
+      <c r="N12" s="35"/>
+      <c r="O12" s="35"/>
+    </row>
+    <row r="13" spans="1:15" ht="83.1" customHeight="1">
+      <c r="H13" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+    </row>
+    <row r="14" spans="1:15" ht="83.1" customHeight="1">
+      <c r="H14" s="35" t="s">
+        <v>195</v>
+      </c>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="35"/>
+    </row>
+    <row r="15" spans="1:15" ht="83.1" customHeight="1">
+      <c r="A15" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="H15" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="I15" s="35"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="35"/>
+    </row>
+    <row r="16" spans="1:15" ht="83.1" customHeight="1">
+      <c r="A16" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H16" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="I16" s="35"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="35"/>
+    </row>
+    <row r="17" spans="1:15" ht="83.1" customHeight="1">
+      <c r="A17" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+    </row>
+    <row r="18" spans="1:15" ht="83.1" customHeight="1">
+      <c r="A18" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="H18" s="35" t="s">
+        <v>193</v>
+      </c>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+    </row>
+    <row r="19" spans="1:15" ht="83.1" customHeight="1">
+      <c r="A19" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="H19" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+    </row>
+    <row r="20" spans="1:15" ht="83.1" customHeight="1">
+      <c r="A20" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="H20" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="35"/>
+    </row>
+    <row r="21" spans="1:15" ht="83.1" customHeight="1">
+      <c r="H21" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+    </row>
+    <row r="22" spans="1:15" ht="83.1" customHeight="1">
+      <c r="H22" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
+    </row>
+    <row r="23" spans="1:15" ht="83.1" customHeight="1">
+      <c r="H23" s="35" t="s">
+        <v>210</v>
+      </c>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+    </row>
+    <row r="24" spans="1:15" ht="72" customHeight="1">
+      <c r="H24" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35"/>
+    </row>
+    <row r="25" spans="1:15" ht="46.5" customHeight="1">
+      <c r="H25" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="23">
+    <mergeCell ref="H23:O23"/>
+    <mergeCell ref="H24:O24"/>
+    <mergeCell ref="H25:O25"/>
+    <mergeCell ref="H20:O20"/>
+    <mergeCell ref="H21:O21"/>
+    <mergeCell ref="H13:O13"/>
+    <mergeCell ref="H4:O4"/>
+    <mergeCell ref="H22:O22"/>
+    <mergeCell ref="H15:O15"/>
+    <mergeCell ref="H16:O16"/>
+    <mergeCell ref="H17:O17"/>
+    <mergeCell ref="H18:O18"/>
+    <mergeCell ref="H19:O19"/>
+    <mergeCell ref="H10:O10"/>
+    <mergeCell ref="H5:O5"/>
+    <mergeCell ref="H11:O11"/>
+    <mergeCell ref="H12:O12"/>
+    <mergeCell ref="H14:O14"/>
     <mergeCell ref="H2:O2"/>
+    <mergeCell ref="H6:O6"/>
+    <mergeCell ref="H7:O7"/>
+    <mergeCell ref="H8:O8"/>
+    <mergeCell ref="H9:O9"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
